--- a/0_SELECT_ZIVE_DATA_2023/AtsisiuntimasZiveDuomenu/Atsisiusti_visi_anotuoti_duomenys/visi_zive_irasai_annot-Darb _atrankai_anotuoti_neliesti.xlsx
+++ b/0_SELECT_ZIVE_DATA_2023/AtsisiuntimasZiveDuomenu/Atsisiusti_visi_anotuoti_duomenys/visi_zive_irasai_annot-Darb _atrankai_anotuoti_neliesti.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\kesju\DI\2025_ZIVEO\PROJECT_TRAIN_UNET\0_SELECT_ZIVE_DATA_2023\AtsisiuntimasZiveDuomenu\Atsisiusti_visi_anotuoti_duomenys\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{511145D2-6173-4895-A79A-2174B4F6F2E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A77A7BA-D726-47D3-929D-416C0EA5059C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,12 +18,25 @@
     <sheet name="Marks" sheetId="3" r:id="rId3"/>
     <sheet name="Notes" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8656" uniqueCount="3899">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8655" uniqueCount="3899">
   <si>
     <t>filename</t>
   </si>
@@ -11758,7 +11771,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -11807,6 +11820,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -11844,7 +11863,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -11906,6 +11925,7 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -24987,10 +25007,10 @@
         <v>0</v>
       </c>
       <c r="E149">
-        <v>11110</v>
+        <v>1111</v>
       </c>
       <c r="G149" t="s">
-        <v>38</v>
+        <v>3724</v>
       </c>
       <c r="H149" s="10">
         <v>634</v>
@@ -92608,11 +92628,11 @@
       <c r="D936">
         <v>0</v>
       </c>
-      <c r="E936" t="s">
-        <v>38</v>
+      <c r="E936">
+        <v>2222</v>
       </c>
       <c r="G936" t="s">
-        <v>38</v>
+        <v>3724</v>
       </c>
       <c r="H936" s="10">
         <v>643</v>
@@ -96921,7 +96941,7 @@
       <c r="D986">
         <v>0</v>
       </c>
-      <c r="E986">
+      <c r="E986" s="27">
         <v>11110</v>
       </c>
       <c r="F986" t="s">
@@ -97269,7 +97289,7 @@
         <v>0</v>
       </c>
       <c r="E990">
-        <v>11110</v>
+        <v>1111</v>
       </c>
       <c r="F990" t="s">
         <v>3742</v>
@@ -97533,7 +97553,7 @@
         <v>0</v>
       </c>
       <c r="E993">
-        <v>3333</v>
+        <v>2222</v>
       </c>
       <c r="F993" t="s">
         <v>3742</v>

--- a/0_SELECT_ZIVE_DATA_2023/AtsisiuntimasZiveDuomenu/Atsisiusti_visi_anotuoti_duomenys/visi_zive_irasai_annot-Darb _atrankai_anotuoti_neliesti.xlsx
+++ b/0_SELECT_ZIVE_DATA_2023/AtsisiuntimasZiveDuomenu/Atsisiusti_visi_anotuoti_duomenys/visi_zive_irasai_annot-Darb _atrankai_anotuoti_neliesti.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\kesju\DI\2025_ZIVEO\PROJECT_TRAIN_UNET\0_SELECT_ZIVE_DATA_2023\AtsisiuntimasZiveDuomenu\Atsisiusti_visi_anotuoti_duomenys\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB76AEB5-4E77-418D-9A48-41F1B8BB3772}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01A1B5C7-FF00-4E7D-8DB3-3F193C7FEE93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17494,7 +17494,7 @@
         <v>1</v>
       </c>
       <c r="E61">
-        <v>2222</v>
+        <v>1111</v>
       </c>
       <c r="G61" t="s">
         <v>3696</v>
